--- a/artfynd/A 7366-2023 artfynd.xlsx
+++ b/artfynd/A 7366-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7366-2023 artfynd.xlsx
+++ b/artfynd/A 7366-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54756201</v>
+        <v>57696351</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98487</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>1860</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Hålrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Aristolochia clematitis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Månkarbo, Upl</t>
+          <t>Skogsby folkhögskola 100 m NO, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637570.320459555</v>
+        <v>637739</v>
       </c>
       <c r="R2" t="n">
-        <v>6677345.502772</v>
+        <v>6677269</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,22 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-08-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-08-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>förv.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,31 +770,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gräsmark intill tomt</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Frisk</t>
+          <t>Jörgen Josefsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Frisk</t>
+          <t>Jörgen Josefsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73686339</v>
+        <v>16895058</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,41 +802,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Månkarbo, Upl</t>
+          <t>Fånbo, S om Månkarbo, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637570.320459555</v>
+        <v>637599</v>
       </c>
       <c r="R3" t="n">
-        <v>6677345.502772</v>
+        <v>6677373</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +856,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-10-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-10-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Kryptogamkurs med Svante Hultengren, Gillis Aronsson och Johan Nitare</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,84 +875,71 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Frisk</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Frisk, Kristina Nygren Frisk</t>
+          <t>Henrik Weibull, Svante Hultengren, Gillis Aronsson, Markus Forsberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87311978</v>
+        <v>68369129</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fiskartorp, Månkarbo S, Upl</t>
+          <t>Fånbo, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637610.2662406168</v>
+        <v>637598</v>
       </c>
       <c r="R4" t="n">
-        <v>6677303.720922998</v>
+        <v>6677369</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,22 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-08-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-11-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-08-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-11-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,22 +977,570 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>16895060</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fånbo, S om Månkarbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>637599</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6677373</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-10-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-10-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kryptogamkurs med Svante Hultengren, Gillis Aronsson och Johan Nitare</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Weibull, Svante Hultengren, Gillis Aronsson, Markus Forsberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16895062</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fånbo, S om Månkarbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>637599</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6677373</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2014-10-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2014-10-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kryptogamkurs med Svante Hultengren, Gillis Aronsson och Johan Nitare</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Åtminstone en bål högt upp på en tall</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henrik Weibull, Svante Hultengren, Gillis Aronsson, Markus Forsberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>87311978</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fiskartorp, Månkarbo S, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>637610</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6677304</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-08-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-08-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Göran Frisk</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Göran Frisk, Kristina Nygren Frisk</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>54756201</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Månkarbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>637570</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6677346</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-08-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-08-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>73686339</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Månkarbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>637570</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6677346</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-10-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-10-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Göran Frisk, Kristina Nygren Frisk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7366-2023 artfynd.xlsx
+++ b/artfynd/A 7366-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57696351</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895058</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68369129</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895060</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895062</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87311978</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54756201</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1541,8 +1581,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73686339</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>